--- a/analysis_history.xlsx
+++ b/analysis_history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,573 @@
           <t>规则分析（离线模式）</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-06 18:35</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>王妈妈</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>询问师资</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>理性分析型</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2-4周（需建立信任，耐心引导）</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 18:45</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王妈妈</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>询问师资</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>理性分析型</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>55</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2-4周（需建立信任，耐心引导）</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 18:55</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>王妈妈</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>询问师资</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>理性分析型</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2-4周（需建立信任，耐心引导）</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 18:57</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>王彬彬</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>中等偏上</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>要求试听</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>价格敏感型</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>58</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2-4周（需建立信任，耐心引导）</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>王彬彬</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>班级前10%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>要求试听</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>价格敏感型</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>69</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1-2周（持续培育，稳步推进）</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>王彬彬</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>班级前10%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>要求试听</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>价格敏感型</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>69</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1-2周（持续培育，稳步推进）</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>王彬彬</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>班级前10%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>要求试听</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>价格敏感型</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>69</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1-2周（持续培育，稳步推进）</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王彬彬</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>询问师资</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>价格敏感型</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2-4周（需建立信任，耐心引导）</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王彬彬</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>询问师资</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>价格敏感型</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2-4周（需建立信任，耐心引导）</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>规则分析（离线模式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>王彬彬</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>提分</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>询问师资</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>价格敏感型 &amp; 提分驱动型</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>45</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1-2周</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AI智能分析（Gemini 2.5 Flash · RAG知识库）</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
